--- a/result/UTS-KOMDAT-JARKOM-K15.xlsx
+++ b/result/UTS-KOMDAT-JARKOM-K15.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\umarb\Documents\kuliah\semester-3\jarkom\MidProject-Jarkom_K15_005_025_055\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\umarb\Documents\kuliah\semester-3\jarkom\MidProject-Jarkom_K15_005_025_055\result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABD55DA-2849-4FEA-A900-9E9F011725A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D08E9A6-5F4D-4F34-B7D7-0BB63671803D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Kelompok" sheetId="1" r:id="rId1"/>
@@ -1551,33 +1551,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1598,14 +1571,41 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="5" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
-      <c r="B5" s="69">
+      <c r="B5" s="60">
         <v>15</v>
       </c>
       <c r="C5" s="56">
@@ -1910,7 +1910,7 @@
     </row>
     <row r="6" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
-      <c r="B6" s="70"/>
+      <c r="B6" s="61"/>
       <c r="C6" s="56">
         <v>5027251025</v>
       </c>
@@ -1920,7 +1920,7 @@
     </row>
     <row r="7" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
-      <c r="B7" s="71"/>
+      <c r="B7" s="62"/>
       <c r="C7" s="56">
         <v>5027251055</v>
       </c>
@@ -1930,8 +1930,8 @@
       <c r="I7" s="7"/>
     </row>
     <row r="10" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B10" s="72"/>
-      <c r="C10" s="73"/>
+      <c r="B10" s="63"/>
+      <c r="C10" s="64"/>
       <c r="D10" s="9"/>
     </row>
     <row r="11" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
@@ -1943,49 +1943,49 @@
       <c r="B12" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="66" t="s">
+      <c r="C12" s="57" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="67"/>
+      <c r="D12" s="58"/>
       <c r="F12" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="66" t="s">
+      <c r="G12" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="67"/>
+      <c r="H12" s="58"/>
     </row>
     <row r="13" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="74" t="s">
+      <c r="C13" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="75"/>
+      <c r="D13" s="66"/>
       <c r="F13" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="G13" s="68" t="s">
+      <c r="G13" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="H13" s="67"/>
+      <c r="H13" s="58"/>
     </row>
     <row r="14" spans="1:9" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="66" t="s">
+      <c r="C14" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="67"/>
+      <c r="D14" s="58"/>
       <c r="F14" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="G14" s="68" t="s">
+      <c r="G14" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="H14" s="67"/>
+      <c r="H14" s="58"/>
     </row>
     <row r="15" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="16" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2530,47 +2530,47 @@
       </c>
     </row>
     <row r="3" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="59" t="s">
+      <c r="C3" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="59" t="s">
+      <c r="D3" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="59" t="s">
+      <c r="E3" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="59" t="s">
+      <c r="F3" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="57" t="s">
+      <c r="G3" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="58"/>
-      <c r="I3" s="59" t="s">
+      <c r="H3" s="72"/>
+      <c r="I3" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="59" t="s">
+      <c r="J3" s="69" t="s">
         <v>22</v>
       </c>
       <c r="K3" s="5"/>
     </row>
     <row r="4" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="60"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
       <c r="G4" s="8" t="s">
         <v>25</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="70"/>
       <c r="K4" s="5"/>
     </row>
     <row r="5" spans="2:11" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -2590,7 +2590,7 @@
       <c r="F5" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="6" t="s">
         <v>42</v>
       </c>
       <c r="H5" s="10" t="s">
@@ -3292,22 +3292,22 @@
       </c>
     </row>
     <row r="31" spans="2:11" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B31" s="61" t="s">
+      <c r="B31" s="73" t="s">
         <v>208</v>
       </c>
-      <c r="C31" s="62"/>
-      <c r="D31" s="62"/>
-      <c r="E31" s="62"/>
-      <c r="F31" s="63"/>
+      <c r="C31" s="74"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="74"/>
+      <c r="F31" s="75"/>
     </row>
     <row r="32" spans="2:11" ht="60" x14ac:dyDescent="0.2">
       <c r="B32" s="6">
         <v>21</v>
       </c>
-      <c r="C32" s="64" t="s">
+      <c r="C32" s="67" t="s">
         <v>210</v>
       </c>
-      <c r="D32" s="65"/>
+      <c r="D32" s="68"/>
       <c r="E32" s="35" t="s">
         <v>212</v>
       </c>
@@ -3319,10 +3319,10 @@
       <c r="B33" s="6">
         <v>22</v>
       </c>
-      <c r="C33" s="64" t="s">
+      <c r="C33" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="D33" s="65"/>
+      <c r="D33" s="68"/>
       <c r="E33" s="35" t="s">
         <v>220</v>
       </c>
@@ -3334,10 +3334,10 @@
       <c r="B34" s="6">
         <v>23</v>
       </c>
-      <c r="C34" s="64" t="s">
+      <c r="C34" s="67" t="s">
         <v>223</v>
       </c>
-      <c r="D34" s="65"/>
+      <c r="D34" s="68"/>
       <c r="E34" s="35" t="s">
         <v>225</v>
       </c>
@@ -3347,18 +3347,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="E3:E4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3374,10 +3374,10 @@
   <cols>
     <col min="2" max="3" width="15.7109375" customWidth="1"/>
     <col min="4" max="4" width="27.5703125" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.5703125" customWidth="1"/>
     <col min="7" max="7" width="32.42578125" customWidth="1"/>
-    <col min="8" max="8" width="16.42578125" customWidth="1"/>
+    <col min="8" max="8" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" customWidth="1"/>
     <col min="10" max="12" width="20.140625" customWidth="1"/>
     <col min="13" max="13" width="22.5703125" customWidth="1"/>
@@ -3458,41 +3458,41 @@
     </row>
     <row r="3" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5"/>
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="59" t="s">
+      <c r="C3" s="69" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="59" t="s">
+      <c r="D3" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="59" t="s">
+      <c r="E3" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="F3" s="59" t="s">
+      <c r="F3" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="G3" s="59" t="s">
+      <c r="G3" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="H3" s="59" t="s">
+      <c r="H3" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="I3" s="59" t="s">
+      <c r="I3" s="69" t="s">
         <v>69</v>
       </c>
-      <c r="J3" s="59" t="s">
+      <c r="J3" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="K3" s="57" t="s">
+      <c r="K3" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="L3" s="67"/>
-      <c r="M3" s="59" t="s">
+      <c r="L3" s="58"/>
+      <c r="M3" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="N3" s="59" t="s">
+      <c r="N3" s="69" t="s">
         <v>22</v>
       </c>
       <c r="O3" s="5"/>
@@ -3517,23 +3517,23 @@
     </row>
     <row r="4" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
       <c r="K4" s="8" t="s">
         <v>25</v>
       </c>
       <c r="L4" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="77"/>
-      <c r="N4" s="77"/>
+      <c r="M4" s="78"/>
+      <c r="N4" s="78"/>
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
@@ -3556,19 +3556,19 @@
     </row>
     <row r="5" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
-      <c r="B5" s="76">
+      <c r="B5" s="79">
         <v>1</v>
       </c>
-      <c r="C5" s="76" t="s">
+      <c r="C5" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="76" t="s">
+      <c r="D5" s="79" t="s">
         <v>95</v>
       </c>
-      <c r="E5" s="78">
+      <c r="E5" s="76">
         <v>17</v>
       </c>
-      <c r="F5" s="76">
+      <c r="F5" s="79">
         <f>2^(32-E5)</f>
         <v>32768</v>
       </c>
@@ -3594,7 +3594,7 @@
       <c r="M5" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="N5" s="76">
+      <c r="N5" s="79">
         <v>0</v>
       </c>
       <c r="O5" s="5"/>
@@ -3619,11 +3619,11 @@
     </row>
     <row r="6" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
-      <c r="B6" s="79"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
+      <c r="B6" s="77"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
       <c r="G6" s="21" t="s">
         <v>101</v>
       </c>
@@ -3646,7 +3646,7 @@
       <c r="M6" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="N6" s="79"/>
+      <c r="N6" s="77"/>
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
@@ -3669,11 +3669,11 @@
     </row>
     <row r="7" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
-      <c r="B7" s="77"/>
-      <c r="C7" s="77"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="77"/>
-      <c r="F7" s="77"/>
+      <c r="B7" s="78"/>
+      <c r="C7" s="78"/>
+      <c r="D7" s="78"/>
+      <c r="E7" s="78"/>
+      <c r="F7" s="78"/>
       <c r="G7" s="23" t="s">
         <v>159</v>
       </c>
@@ -3695,7 +3695,7 @@
       <c r="M7" s="26" t="s">
         <v>175</v>
       </c>
-      <c r="N7" s="77"/>
+      <c r="N7" s="78"/>
       <c r="O7" s="5"/>
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
@@ -3718,19 +3718,19 @@
     </row>
     <row r="8" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
-      <c r="B8" s="76">
+      <c r="B8" s="79">
         <v>2</v>
       </c>
-      <c r="C8" s="76" t="s">
+      <c r="C8" s="79" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="76" t="s">
+      <c r="D8" s="79" t="s">
         <v>180</v>
       </c>
-      <c r="E8" s="78">
+      <c r="E8" s="76">
         <v>18</v>
       </c>
-      <c r="F8" s="76">
+      <c r="F8" s="79">
         <f>2^(32-E8)</f>
         <v>16384</v>
       </c>
@@ -3756,7 +3756,7 @@
       <c r="M8" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="N8" s="76">
+      <c r="N8" s="79">
         <f>N5+F5</f>
         <v>32768</v>
       </c>
@@ -3782,11 +3782,11 @@
     </row>
     <row r="9" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
-      <c r="B9" s="79"/>
-      <c r="C9" s="79"/>
-      <c r="D9" s="79"/>
-      <c r="E9" s="79"/>
-      <c r="F9" s="79"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
       <c r="G9" s="28" t="s">
         <v>126</v>
       </c>
@@ -3809,7 +3809,7 @@
       <c r="M9" s="22" t="s">
         <v>207</v>
       </c>
-      <c r="N9" s="79"/>
+      <c r="N9" s="77"/>
       <c r="O9" s="5"/>
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
@@ -3832,11 +3832,11 @@
     </row>
     <row r="10" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
+      <c r="B10" s="78"/>
+      <c r="C10" s="78"/>
+      <c r="D10" s="78"/>
+      <c r="E10" s="78"/>
+      <c r="F10" s="78"/>
       <c r="G10" s="36" t="s">
         <v>211</v>
       </c>
@@ -3858,7 +3858,7 @@
       <c r="M10" s="26" t="s">
         <v>219</v>
       </c>
-      <c r="N10" s="77"/>
+      <c r="N10" s="78"/>
       <c r="O10" s="5"/>
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
@@ -3881,19 +3881,19 @@
     </row>
     <row r="11" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
-      <c r="B11" s="76">
+      <c r="B11" s="79">
         <v>3</v>
       </c>
-      <c r="C11" s="76" t="s">
+      <c r="C11" s="79" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="76" t="s">
+      <c r="D11" s="79" t="s">
         <v>227</v>
       </c>
-      <c r="E11" s="78">
+      <c r="E11" s="76">
         <v>18</v>
       </c>
-      <c r="F11" s="76">
+      <c r="F11" s="79">
         <f>2^(32-E11)</f>
         <v>16384</v>
       </c>
@@ -3919,7 +3919,7 @@
       <c r="M11" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="N11" s="76">
+      <c r="N11" s="79">
         <f>N8+F8</f>
         <v>49152</v>
       </c>
@@ -3945,11 +3945,11 @@
     </row>
     <row r="12" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
-      <c r="B12" s="79"/>
-      <c r="C12" s="79"/>
-      <c r="D12" s="79"/>
-      <c r="E12" s="79"/>
-      <c r="F12" s="79"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
       <c r="G12" s="28" t="s">
         <v>115</v>
       </c>
@@ -3972,7 +3972,7 @@
       <c r="M12" s="22" t="s">
         <v>238</v>
       </c>
-      <c r="N12" s="79"/>
+      <c r="N12" s="77"/>
       <c r="O12" s="5"/>
       <c r="P12" s="5"/>
       <c r="Q12" s="5"/>
@@ -3995,11 +3995,11 @@
     </row>
     <row r="13" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
-      <c r="B13" s="77"/>
-      <c r="C13" s="77"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
+      <c r="B13" s="78"/>
+      <c r="C13" s="78"/>
+      <c r="D13" s="78"/>
+      <c r="E13" s="78"/>
+      <c r="F13" s="78"/>
       <c r="G13" s="36" t="s">
         <v>247</v>
       </c>
@@ -4021,7 +4021,7 @@
       <c r="M13" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="N13" s="77"/>
+      <c r="N13" s="78"/>
       <c r="O13" s="5"/>
       <c r="P13" s="5"/>
       <c r="Q13" s="5"/>
@@ -4044,19 +4044,19 @@
     </row>
     <row r="14" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
-      <c r="B14" s="76">
+      <c r="B14" s="79">
         <v>4</v>
       </c>
-      <c r="C14" s="76" t="s">
+      <c r="C14" s="79" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="76" t="s">
+      <c r="D14" s="79" t="s">
         <v>252</v>
       </c>
-      <c r="E14" s="78">
+      <c r="E14" s="76">
         <v>18</v>
       </c>
-      <c r="F14" s="76">
+      <c r="F14" s="79">
         <f>2^(32-E14)</f>
         <v>16384</v>
       </c>
@@ -4082,7 +4082,7 @@
       <c r="M14" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="N14" s="76">
+      <c r="N14" s="79">
         <f>N11+F11</f>
         <v>65536</v>
       </c>
@@ -4108,11 +4108,11 @@
     </row>
     <row r="15" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="79"/>
-      <c r="C15" s="79"/>
-      <c r="D15" s="79"/>
-      <c r="E15" s="79"/>
-      <c r="F15" s="79"/>
+      <c r="B15" s="77"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="77"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="77"/>
       <c r="G15" s="28" t="s">
         <v>94</v>
       </c>
@@ -4135,7 +4135,7 @@
       <c r="M15" s="22" t="s">
         <v>260</v>
       </c>
-      <c r="N15" s="79"/>
+      <c r="N15" s="77"/>
       <c r="O15" s="5"/>
       <c r="P15" s="5"/>
       <c r="Q15" s="5"/>
@@ -4158,11 +4158,11 @@
     </row>
     <row r="16" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
-      <c r="B16" s="77"/>
-      <c r="C16" s="77"/>
-      <c r="D16" s="77"/>
-      <c r="E16" s="77"/>
-      <c r="F16" s="77"/>
+      <c r="B16" s="78"/>
+      <c r="C16" s="78"/>
+      <c r="D16" s="78"/>
+      <c r="E16" s="78"/>
+      <c r="F16" s="78"/>
       <c r="G16" s="36" t="s">
         <v>261</v>
       </c>
@@ -4184,7 +4184,7 @@
       <c r="M16" s="26" t="s">
         <v>265</v>
       </c>
-      <c r="N16" s="77"/>
+      <c r="N16" s="78"/>
       <c r="O16" s="5"/>
       <c r="P16" s="5"/>
       <c r="Q16" s="5"/>
@@ -4207,19 +4207,19 @@
     </row>
     <row r="17" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
-      <c r="B17" s="76">
+      <c r="B17" s="79">
         <v>5</v>
       </c>
-      <c r="C17" s="76" t="s">
+      <c r="C17" s="79" t="s">
         <v>71</v>
       </c>
-      <c r="D17" s="76" t="s">
+      <c r="D17" s="79" t="s">
         <v>266</v>
       </c>
-      <c r="E17" s="78">
+      <c r="E17" s="76">
         <v>18</v>
       </c>
-      <c r="F17" s="76">
+      <c r="F17" s="79">
         <f>2^(32-E17)</f>
         <v>16384</v>
       </c>
@@ -4245,7 +4245,7 @@
       <c r="M17" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="N17" s="76">
+      <c r="N17" s="79">
         <f>N14+F14</f>
         <v>81920</v>
       </c>
@@ -4271,11 +4271,11 @@
     </row>
     <row r="18" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
-      <c r="B18" s="79"/>
-      <c r="C18" s="79"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="79"/>
-      <c r="F18" s="79"/>
+      <c r="B18" s="77"/>
+      <c r="C18" s="77"/>
+      <c r="D18" s="77"/>
+      <c r="E18" s="77"/>
+      <c r="F18" s="77"/>
       <c r="G18" s="28" t="s">
         <v>121</v>
       </c>
@@ -4298,7 +4298,7 @@
       <c r="M18" s="22" t="s">
         <v>274</v>
       </c>
-      <c r="N18" s="79"/>
+      <c r="N18" s="77"/>
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
       <c r="Q18" s="5"/>
@@ -4321,11 +4321,11 @@
     </row>
     <row r="19" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
-      <c r="B19" s="77"/>
-      <c r="C19" s="77"/>
-      <c r="D19" s="77"/>
-      <c r="E19" s="77"/>
-      <c r="F19" s="77"/>
+      <c r="B19" s="78"/>
+      <c r="C19" s="78"/>
+      <c r="D19" s="78"/>
+      <c r="E19" s="78"/>
+      <c r="F19" s="78"/>
       <c r="G19" s="36" t="s">
         <v>275</v>
       </c>
@@ -4347,7 +4347,7 @@
       <c r="M19" s="26" t="s">
         <v>279</v>
       </c>
-      <c r="N19" s="77"/>
+      <c r="N19" s="78"/>
       <c r="O19" s="5"/>
       <c r="P19" s="5"/>
       <c r="Q19" s="5"/>
@@ -4370,19 +4370,19 @@
     </row>
     <row r="20" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
-      <c r="B20" s="76">
+      <c r="B20" s="79">
         <v>6</v>
       </c>
-      <c r="C20" s="76" t="s">
+      <c r="C20" s="79" t="s">
         <v>80</v>
       </c>
-      <c r="D20" s="76" t="s">
+      <c r="D20" s="79" t="s">
         <v>280</v>
       </c>
-      <c r="E20" s="78">
+      <c r="E20" s="76">
         <v>18</v>
       </c>
-      <c r="F20" s="76">
+      <c r="F20" s="79">
         <f>2^(32-E20)</f>
         <v>16384</v>
       </c>
@@ -4408,7 +4408,7 @@
       <c r="M20" s="20" t="s">
         <v>284</v>
       </c>
-      <c r="N20" s="76">
+      <c r="N20" s="79">
         <f>N17+F17</f>
         <v>98304</v>
       </c>
@@ -4434,11 +4434,11 @@
     </row>
     <row r="21" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
-      <c r="B21" s="79"/>
-      <c r="C21" s="79"/>
-      <c r="D21" s="79"/>
-      <c r="E21" s="79"/>
-      <c r="F21" s="79"/>
+      <c r="B21" s="77"/>
+      <c r="C21" s="77"/>
+      <c r="D21" s="77"/>
+      <c r="E21" s="77"/>
+      <c r="F21" s="77"/>
       <c r="G21" s="28" t="s">
         <v>108</v>
       </c>
@@ -4461,7 +4461,7 @@
       <c r="M21" s="22" t="s">
         <v>288</v>
       </c>
-      <c r="N21" s="79"/>
+      <c r="N21" s="77"/>
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
       <c r="Q21" s="5"/>
@@ -4484,11 +4484,11 @@
     </row>
     <row r="22" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
-      <c r="B22" s="77"/>
-      <c r="C22" s="77"/>
-      <c r="D22" s="77"/>
-      <c r="E22" s="77"/>
-      <c r="F22" s="77"/>
+      <c r="B22" s="78"/>
+      <c r="C22" s="78"/>
+      <c r="D22" s="78"/>
+      <c r="E22" s="78"/>
+      <c r="F22" s="78"/>
       <c r="G22" s="36" t="s">
         <v>289</v>
       </c>
@@ -4510,7 +4510,7 @@
       <c r="M22" s="26" t="s">
         <v>293</v>
       </c>
-      <c r="N22" s="77"/>
+      <c r="N22" s="78"/>
       <c r="O22" s="5"/>
       <c r="P22" s="5"/>
       <c r="Q22" s="5"/>
@@ -4533,19 +4533,19 @@
     </row>
     <row r="23" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
-      <c r="B23" s="76">
+      <c r="B23" s="79">
         <v>7</v>
       </c>
-      <c r="C23" s="76" t="s">
+      <c r="C23" s="79" t="s">
         <v>87</v>
       </c>
-      <c r="D23" s="76" t="s">
+      <c r="D23" s="79" t="s">
         <v>294</v>
       </c>
-      <c r="E23" s="78">
+      <c r="E23" s="76">
         <v>20</v>
       </c>
-      <c r="F23" s="76">
+      <c r="F23" s="79">
         <f>2^(32-E23)</f>
         <v>4096</v>
       </c>
@@ -4571,7 +4571,7 @@
       <c r="M23" s="43" t="s">
         <v>298</v>
       </c>
-      <c r="N23" s="76">
+      <c r="N23" s="79">
         <f>N20+F20</f>
         <v>114688</v>
       </c>
@@ -4597,11 +4597,11 @@
     </row>
     <row r="24" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
-      <c r="B24" s="77"/>
-      <c r="C24" s="77"/>
-      <c r="D24" s="77"/>
-      <c r="E24" s="77"/>
-      <c r="F24" s="77"/>
+      <c r="B24" s="78"/>
+      <c r="C24" s="78"/>
+      <c r="D24" s="78"/>
+      <c r="E24" s="78"/>
+      <c r="F24" s="78"/>
       <c r="G24" s="36" t="s">
         <v>131</v>
       </c>
@@ -4624,7 +4624,7 @@
       <c r="M24" s="44" t="s">
         <v>302</v>
       </c>
-      <c r="N24" s="77"/>
+      <c r="N24" s="78"/>
       <c r="O24" s="5"/>
       <c r="P24" s="5"/>
       <c r="Q24" s="5"/>
@@ -38839,6 +38839,50 @@
     </row>
   </sheetData>
   <mergeCells count="54">
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="N20:N22"/>
+    <mergeCell ref="N23:N24"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="N5:N7"/>
+    <mergeCell ref="N8:N10"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="N11:N13"/>
+    <mergeCell ref="N14:N16"/>
+    <mergeCell ref="N17:N19"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
     <mergeCell ref="E20:E22"/>
     <mergeCell ref="F20:F22"/>
     <mergeCell ref="C17:C19"/>
@@ -38849,50 +38893,6 @@
     <mergeCell ref="F17:F19"/>
     <mergeCell ref="C20:C22"/>
     <mergeCell ref="D20:D22"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="E11:E13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="N11:N13"/>
-    <mergeCell ref="N14:N16"/>
-    <mergeCell ref="N17:N19"/>
-    <mergeCell ref="N20:N22"/>
-    <mergeCell ref="N23:N24"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="N5:N7"/>
-    <mergeCell ref="N8:N10"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="F23:F24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -38917,18 +38917,18 @@
       <c r="B3" s="83" t="s">
         <v>181</v>
       </c>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
       <c r="H3" s="14"/>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B5" s="84" t="s">
         <v>183</v>
       </c>
-      <c r="C5" s="67"/>
+      <c r="C5" s="58"/>
       <c r="D5" s="29" t="s">
         <v>185</v>
       </c>
@@ -38938,7 +38938,7 @@
       <c r="F5" s="84" t="s">
         <v>187</v>
       </c>
-      <c r="G5" s="67"/>
+      <c r="G5" s="58"/>
     </row>
     <row r="6" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="85" t="s">
@@ -39127,8 +39127,8 @@
       <c r="A1" s="90" t="s">
         <v>228</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
     </row>
     <row r="3" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B3" s="88" t="s">
